--- a/S1_confirmatory_search_screening.xlsx
+++ b/S1_confirmatory_search_screening.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Already in the corpus as [116].</t>
+          <t>Already in the corpus as [88].</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Already in the corpus as [117].</t>
+          <t>Already in the corpus as [89].</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Already in the corpus as [80].</t>
+          <t>Already in the corpus as [84].</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Already in the corpus as [81].</t>
+          <t>Already in the corpus as [85].</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Already in the corpus as [122].</t>
+          <t>Already in the corpus as [91].</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Already in the corpus as [110].</t>
+          <t>Already in the corpus as [87].</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Earlier version of [81]</t>
+          <t>Earlier version of [85]</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Conference version of [81].</t>
+          <t>Conference version of [85].</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Earlier version of [109]</t>
+          <t>Earlier version of [86]</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Conference version of [109].</t>
+          <t>Conference version of [86].</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Earlier version of [116]</t>
+          <t>Earlier version of [88]</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Conference version of [116].</t>
+          <t>Conference version of [88].</t>
         </is>
       </c>
     </row>
